--- a/data/trans_dic/P1409-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P1409-Habitat-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,13</t>
+          <t>1,03; 3,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,05; 4,86</t>
+          <t>2,02; 4,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,18; 7,2</t>
+          <t>3,11; 6,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,73</t>
+          <t>1,36; 3,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,19; 5,09</t>
+          <t>2,2; 5,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,43; 4,42</t>
+          <t>2,26; 4,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,91</t>
+          <t>1,41; 3,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 4,5</t>
+          <t>2,42; 4,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,07; 5,4</t>
+          <t>2,96; 5,01</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,73</t>
+          <t>1,11; 2,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,44</t>
+          <t>1,48; 3,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 5,83</t>
+          <t>3,12; 6,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,15</t>
+          <t>1,81; 4,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,23; 6,13</t>
+          <t>3,16; 5,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,97; 5,06</t>
+          <t>2,99; 4,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,04</t>
+          <t>1,7; 3,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,6; 4,23</t>
+          <t>2,63; 4,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,52; 5,06</t>
+          <t>3,4; 5,32</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,22</t>
+          <t>0,68; 2,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,55</t>
+          <t>0,81; 2,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 6,03</t>
+          <t>1,78; 4,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,85</t>
+          <t>1,45; 3,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,72; 5,52</t>
+          <t>2,68; 5,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 5,65</t>
+          <t>4,32; 7,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,69</t>
+          <t>1,29; 2,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,98; 3,67</t>
+          <t>1,93; 3,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,4; 4,88</t>
+          <t>3,32; 5,32</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,76</t>
+          <t>1,69; 3,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,6</t>
+          <t>2,2; 4,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,5</t>
+          <t>2,31; 4,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,04; 4,33</t>
+          <t>2,1; 4,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,89; 5,45</t>
+          <t>2,87; 5,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,71; 29,61</t>
+          <t>5,01; 7,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,09; 3,64</t>
+          <t>2,14; 3,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,76; 4,47</t>
+          <t>2,78; 4,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,43; 19,62</t>
+          <t>4,0; 5,81</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,5; 2,48</t>
+          <t>1,48; 2,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,13</t>
+          <t>2,02; 3,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,76; 4,61</t>
+          <t>3,16; 4,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,2; 3,37</t>
+          <t>2,19; 3,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,36; 4,69</t>
+          <t>3,38; 4,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,17; 13,9</t>
+          <t>4,25; 5,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,99; 2,73</t>
+          <t>2,0; 2,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,88; 3,75</t>
+          <t>2,86; 3,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,85; 8,73</t>
+          <t>3,88; 4,82</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30458</t>
+          <t>31405</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22104</t>
+          <t>22810</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>52562</t>
+          <t>54215</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7660; 22011</t>
+          <t>7243; 22631</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13827; 32777</t>
+          <t>13616; 32740</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20232; 45731</t>
+          <t>21453; 46609</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9553; 25973</t>
+          <t>9494; 26888</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14717; 34217</t>
+          <t>14786; 33957</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16372; 29796</t>
+          <t>16582; 30648</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19605; 40689</t>
+          <t>19726; 42270</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>32976; 60696</t>
+          <t>32631; 59812</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>40254; 70713</t>
+          <t>42155; 71332</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45128</t>
+          <t>48842</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37727</t>
+          <t>41477</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>82855</t>
+          <t>90319</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10216; 27775</t>
+          <t>11304; 28080</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14756; 35138</t>
+          <t>15111; 33421</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21217; 69487</t>
+          <t>32704; 69058</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19409; 42625</t>
+          <t>18626; 42460</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33708; 63929</t>
+          <t>32997; 61516</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28448; 48433</t>
+          <t>32010; 52925</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33568; 62233</t>
+          <t>34793; 61955</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>53662; 87388</t>
+          <t>54225; 89550</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>54176; 108829</t>
+          <t>72067; 112565</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23309</t>
+          <t>23500</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36744</t>
+          <t>43954</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>60053</t>
+          <t>67454</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4849; 16814</t>
+          <t>5120; 17773</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5996; 19356</t>
+          <t>6155; 20004</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14464; 42308</t>
+          <t>14224; 38381</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11542; 29946</t>
+          <t>11266; 29750</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>21320; 43344</t>
+          <t>21004; 42964</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19608; 52620</t>
+          <t>34992; 57190</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18860; 41218</t>
+          <t>19766; 42607</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>30582; 56638</t>
+          <t>29785; 54572</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>39298; 79801</t>
+          <t>53402; 85601</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28381</t>
+          <t>32134</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>132773</t>
+          <t>69456</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>161154</t>
+          <t>101590</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15580; 35616</t>
+          <t>16002; 36942</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20624; 43083</t>
+          <t>20634; 43655</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19254; 41702</t>
+          <t>22839; 46863</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21442; 45497</t>
+          <t>22096; 44369</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30170; 56930</t>
+          <t>29961; 56440</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>62302; 323035</t>
+          <t>55916; 83991</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>41831; 72880</t>
+          <t>42828; 74388</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>54722; 88495</t>
+          <t>55140; 89517</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>89403; 395814</t>
+          <t>84261; 122394</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>127276</t>
+          <t>135881</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>229348</t>
+          <t>177696</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>356624</t>
+          <t>313578</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>51408; 84834</t>
+          <t>50578; 83690</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>68851; 106386</t>
+          <t>68484; 106829</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>95309; 159198</t>
+          <t>111411; 165220</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>78185; 119660</t>
+          <t>77982; 119290</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>119238; 166235</t>
+          <t>119676; 166461</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>152418; 508248</t>
+          <t>158583; 200886</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>139010; 190369</t>
+          <t>139304; 190443</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>200126; 260204</t>
+          <t>198200; 259201</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>273464; 620534</t>
+          <t>281706; 349650</t>
         </is>
       </c>
     </row>
